--- a/section9_kinetics/C18/general_catalysis_analysis.xlsx
+++ b/section9_kinetics/C18/general_catalysis_analysis.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefan/Documents/Publikationen/06:25/WaterHTE/WaterHTE/section9_kinetics/C18/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55EAD483-9D51-1C47-AB60-5F087B836349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="195">
   <si>
     <t>ha_type</t>
   </si>
@@ -604,8 +623,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -657,24 +676,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -712,7 +740,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -746,6 +774,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -780,9 +809,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -955,11 +985,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1003,12 +1033,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>2.314</v>
+        <v>2.3140000000000001</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
@@ -1047,12 +1077,12 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>3.4143</v>
+        <v>3.4142999999999999</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
@@ -1091,12 +1121,12 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>3.614</v>
+        <v>3.6139999999999999</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
@@ -1135,12 +1165,12 @@
         <v>192</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
       <c r="B5">
-        <v>3.674</v>
+        <v>3.6739999999999999</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
@@ -1179,12 +1209,12 @@
         <v>192</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
       <c r="B6">
-        <v>4.604299999999999</v>
+        <v>4.6042999999999994</v>
       </c>
       <c r="C6" t="s">
         <v>36</v>
@@ -1223,12 +1253,12 @@
         <v>192</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
       <c r="B7">
-        <v>5.143</v>
+        <v>5.1429999999999998</v>
       </c>
       <c r="C7" t="s">
         <v>37</v>
@@ -1263,16 +1293,16 @@
       <c r="M7" t="s">
         <v>191</v>
       </c>
-      <c r="N7" t="s">
-        <v>192</v>
+      <c r="N7" s="2">
+        <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
       <c r="B8">
-        <v>7.105700000000001</v>
+        <v>7.1057000000000006</v>
       </c>
       <c r="C8" t="s">
         <v>38</v>
@@ -1311,12 +1341,12 @@
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9">
-        <v>7.4057</v>
+        <v>7.4057000000000004</v>
       </c>
       <c r="C9" t="s">
         <v>39</v>
@@ -1355,12 +1385,12 @@
         <v>191</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
       <c r="B10">
-        <v>9.074</v>
+        <v>9.0739999999999998</v>
       </c>
       <c r="C10" t="s">
         <v>40</v>
@@ -1395,16 +1425,16 @@
       <c r="M10" t="s">
         <v>191</v>
       </c>
-      <c r="N10" t="s">
-        <v>192</v>
+      <c r="N10" s="2">
+        <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>23</v>
       </c>
       <c r="B11">
-        <v>9.234300000000001</v>
+        <v>9.2343000000000011</v>
       </c>
       <c r="C11" t="s">
         <v>41</v>
@@ -1443,12 +1473,12 @@
         <v>191</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>24</v>
       </c>
       <c r="B12">
-        <v>9.7829</v>
+        <v>9.7828999999999997</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
@@ -1487,12 +1517,12 @@
         <v>193</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13">
-        <v>11.5515</v>
+        <v>11.551500000000001</v>
       </c>
       <c r="C13" t="s">
         <v>43</v>
@@ -1531,12 +1561,12 @@
         <v>194</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
       <c r="B14">
-        <v>12.2343</v>
+        <v>12.234299999999999</v>
       </c>
       <c r="C14" t="s">
         <v>44</v>
@@ -1575,12 +1605,12 @@
         <v>191</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>27</v>
       </c>
       <c r="B15">
-        <v>12.2443</v>
+        <v>12.244300000000001</v>
       </c>
       <c r="C15" t="s">
         <v>45</v>
@@ -1619,7 +1649,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1663,7 +1693,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1707,7 +1737,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -1751,7 +1781,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>31</v>
       </c>
